--- a/Table/Excel/Text_World.xlsx
+++ b/Table/Excel/Text_World.xlsx
@@ -166,8 +166,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_World" displayName="Text_World" ref="B2:E6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:E6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_World" displayName="Text_World" ref="B2:E8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:E8"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key" dataDxfId="3"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E6"/>
+  <dimension ref="B2:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="3.125" customWidth="1" style="3" min="1" max="1"/>
@@ -538,7 +538,7 @@
       <c r="E4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="n">
+      <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -574,6 +574,46 @@
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>world.vending_roulette.title</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>자판기</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Vending Machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>world.vending_roulette.prompt</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>버튼 누르기</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Press a button</t>
         </is>
       </c>
     </row>

--- a/Table/Excel/Text_World.xlsx
+++ b/Table/Excel/Text_World.xlsx
@@ -166,8 +166,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_World" displayName="Text_World" ref="B2:E8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:E8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_World" displayName="Text_World" ref="B2:E10" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:E10"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key" dataDxfId="3"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E8"/>
+  <dimension ref="B2:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="3.125" customWidth="1" style="3" min="1" max="1"/>
@@ -578,7 +578,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="n">
+      <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="n">
+      <c r="B8" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -616,6 +616,38 @@
           <t>Press a button</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>world.jump_rope.title</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>줄넘기</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>world.jump_rope.prompt</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>줄넘기 하기</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
